--- a/data.xlsx
+++ b/data.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="204">
   <si>
     <t>注：填充色为浅黄色的单元格需要手动查找数据填充，其余数据从MSSP平台导出底数据后覆盖子表内容，再更新单元格L1和M1自动按照统计周期计算结果；</t>
   </si>
@@ -650,6 +650,9 @@
   </si>
   <si>
     <t>事件定性分布</t>
+  </si>
+  <si>
+    <t>处置安全事件总数</t>
   </si>
 </sst>
 </file>
@@ -2331,7 +2334,7 @@
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="21" t="s">
-        <v>19</v>
+        <v>203</v>
       </c>
       <c r="G8" s="23"/>
       <c r="K8" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,23 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="22188" windowHeight="9180" firstSheet="1"/>
   </bookViews>
   <sheets>
     <sheet name="数据统计" sheetId="2" r:id="rId1"/>
     <sheet name="暴露面" sheetId="13" r:id="rId2"/>
-    <sheet name="资产漏洞表" sheetId="5" r:id="rId3"/>
-    <sheet name="资产表" sheetId="10" r:id="rId4"/>
-    <sheet name="告警表" sheetId="14" r:id="rId5"/>
-    <sheet name="事件表" sheetId="6" r:id="rId6"/>
-    <sheet name="弱密码表" sheetId="15" r:id="rId7"/>
+    <sheet name="内网漏洞表" sheetId="5" r:id="rId3"/>
+    <sheet name="互联网漏洞表" sheetId="16" r:id="rId4"/>
+    <sheet name="资产表" sheetId="10" r:id="rId5"/>
+    <sheet name="告警表" sheetId="14" r:id="rId6"/>
+    <sheet name="事件表" sheetId="6" r:id="rId7"/>
+    <sheet name="内网弱密码表" sheetId="15" r:id="rId8"/>
+    <sheet name="互联网弱密码表" sheetId="17" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">暴露面!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">资产漏洞表!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">资产表!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">告警表!#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">事件表!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">内网漏洞表!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">资产表!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">告警表!#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">事件表!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,12 +42,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="204">
-  <si>
-    <t>注：填充色为浅黄色的单元格需要手动查找数据填充，其余数据从MSSP平台导出底数据后覆盖子表内容，再更新单元格L1和M1自动按照统计周期计算结果；</t>
-  </si>
-  <si>
-    <t>当前时间</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="199">
+  <si>
+    <t>注：填充色为浅黄色的单元格需要手动查找数据填充</t>
   </si>
   <si>
     <t>统计周期</t>
@@ -63,10 +62,10 @@
     <t>威胁运营</t>
   </si>
   <si>
-    <t>重保时间周期</t>
-  </si>
-  <si>
-    <t>护网，可选，固定此格，来源提示词</t>
+    <t>护网时间</t>
+  </si>
+  <si>
+    <t>用户传入的护网时间，可选</t>
   </si>
   <si>
     <t>手写-系统2</t>
@@ -75,8 +74,14 @@
     <t>安全策略调优数量</t>
   </si>
   <si>
+    <t>手写-策略调优数量</t>
+  </si>
+  <si>
+    <t>时间内节假日</t>
+  </si>
+  <si>
     <t>其余假日：时间范围
-中秋、国庆。元旦、春节、清明、五一、端午</t>
+中秋、国庆、元旦、春节、清明、五一、端午（展示最多一年内的七个法定节假日）</t>
   </si>
   <si>
     <t>手写-系统3</t>
@@ -100,159 +105,156 @@
     <t>威胁平均遏制时间</t>
   </si>
   <si>
+    <t>处置安全事件总数</t>
+  </si>
+  <si>
+    <t>事件平均响应时长</t>
+  </si>
+  <si>
+    <t>高危可利用漏洞数</t>
+  </si>
+  <si>
+    <t>核心系统事件数量</t>
+  </si>
+  <si>
+    <t>管理员弱口令数量</t>
+  </si>
+  <si>
+    <t>最新漏洞影响资产数</t>
+  </si>
+  <si>
+    <t>核心系统风险总数</t>
+  </si>
+  <si>
+    <t>已闭环风险数</t>
+  </si>
+  <si>
+    <t>核心系统风险闭环风险数</t>
+  </si>
+  <si>
+    <t>已防护漏洞数</t>
+  </si>
+  <si>
+    <t>核心系统威胁事件总数</t>
+  </si>
+  <si>
+    <t>已修复漏洞数</t>
+  </si>
+  <si>
+    <t>已处置弱口令数量</t>
+  </si>
+  <si>
+    <t>业务系统数量</t>
+  </si>
+  <si>
+    <t>受影响的最新漏洞数</t>
+  </si>
+  <si>
+    <t>服务器资产数量</t>
+  </si>
+  <si>
+    <t>系统X已闭环风险数</t>
+  </si>
+  <si>
+    <t>PC资产数量</t>
+  </si>
+  <si>
+    <t>P14</t>
+  </si>
+  <si>
+    <t>被通报风险总数</t>
+  </si>
+  <si>
+    <t>通报风险应对</t>
+  </si>
+  <si>
+    <t>外联通报风险次数</t>
+  </si>
+  <si>
+    <t>漏扫次数</t>
+  </si>
+  <si>
+    <t>手写-漏扫次数</t>
+  </si>
+  <si>
+    <t>已闭环漏洞总数</t>
+  </si>
+  <si>
+    <t>已拦截外联次数</t>
+  </si>
+  <si>
+    <t>恶意外联告警数</t>
+  </si>
+  <si>
+    <t>本次汇报周期被通报次数</t>
+  </si>
+  <si>
+    <t>手写-被通报次数</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>「重要时期安全日志数」</t>
+  </si>
+  <si>
+    <t>节假日，不算护网时间</t>
+  </si>
+  <si>
+    <t>重要时期保障</t>
+  </si>
+  <si>
+    <t>「重要时期告警数」</t>
+  </si>
+  <si>
+    <t>「重要时期事件数」</t>
+  </si>
+  <si>
+    <t>重大事故数</t>
+  </si>
+  <si>
+    <t>手写-重大事故数</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>资产覆盖率</t>
+  </si>
+  <si>
+    <t>默认100%</t>
+  </si>
+  <si>
+    <t>威胁遏制率</t>
+  </si>
+  <si>
+    <t>高危漏洞防护率</t>
+  </si>
+  <si>
+    <t>平均分析时间</t>
+  </si>
+  <si>
+    <t>平均响应时间</t>
+  </si>
+  <si>
+    <t>已闭环漏洞数量</t>
+  </si>
+  <si>
+    <t>威胁和事件数量</t>
+  </si>
+  <si>
+    <t>两名高级安全工程师成本</t>
+  </si>
+  <si>
+    <t>手写-两名高级安全工程师成本</t>
+  </si>
+  <si>
+    <t>P35</t>
+  </si>
+  <si>
     <t>安全事件总数</t>
   </si>
   <si>
-    <t>事件平均响应时长</t>
-  </si>
-  <si>
-    <t>高危可利用漏洞数</t>
-  </si>
-  <si>
-    <t>提取管理员弱口令数量</t>
-  </si>
-  <si>
-    <t>核心系统事件数量</t>
-  </si>
-  <si>
-    <t>管理员弱口令数量</t>
-  </si>
-  <si>
-    <t>最新漏洞影响资产数</t>
-  </si>
-  <si>
-    <t>提取事件表中未公开威胁类型工单中受影响资产的IP数量，1.1.1.1,2.2.2.2.这就是两个</t>
-  </si>
-  <si>
-    <t>核心系统风险总数</t>
-  </si>
-  <si>
-    <t>已闭环风险数</t>
-  </si>
-  <si>
-    <t>核心系统风险闭环风险数</t>
-  </si>
-  <si>
-    <t>已防护漏洞数</t>
-  </si>
-  <si>
-    <t>核心系统威胁事件总数</t>
-  </si>
-  <si>
-    <t>已修复漏洞数</t>
-  </si>
-  <si>
-    <t>提取事件表中未公开威胁类型工单中受影响资产的IP数量</t>
-  </si>
-  <si>
-    <t>已处置弱口令数量</t>
-  </si>
-  <si>
-    <t>业务系统数量</t>
-  </si>
-  <si>
-    <t>受影响的最新漏洞数</t>
-  </si>
-  <si>
-    <t>服务器资产数量</t>
-  </si>
-  <si>
-    <t>系统X已闭环风险数</t>
-  </si>
-  <si>
-    <t>PC资产数量</t>
-  </si>
-  <si>
-    <t>P14</t>
-  </si>
-  <si>
-    <t>被通报风险总数</t>
-  </si>
-  <si>
-    <t>通报风险应对</t>
-  </si>
-  <si>
-    <t>外联通报风险次数</t>
-  </si>
-  <si>
-    <t>漏扫次数</t>
-  </si>
-  <si>
-    <t>已闭环漏洞总数</t>
-  </si>
-  <si>
-    <t>已拦截外联次数</t>
-  </si>
-  <si>
-    <t>恶意外联告警数</t>
-  </si>
-  <si>
-    <t>本次汇报周期被通报次数</t>
-  </si>
-  <si>
-    <t>P16</t>
-  </si>
-  <si>
-    <t>「重要时期安全日志数」</t>
-  </si>
-  <si>
-    <t>重保周期+重要节假日</t>
-  </si>
-  <si>
-    <t>只统计安全告警日志，选择时间，取总数，超过六个月取不到</t>
-  </si>
-  <si>
-    <t>重要时期保障</t>
-  </si>
-  <si>
-    <t>「重要时期告警数」</t>
-  </si>
-  <si>
-    <t>告警表在重保时间范围的</t>
-  </si>
-  <si>
-    <t>「重要时期事件数」</t>
-  </si>
-  <si>
-    <t>时间表在重保时间范围的</t>
-  </si>
-  <si>
-    <t>重大事故数</t>
-  </si>
-  <si>
-    <t>P19</t>
-  </si>
-  <si>
-    <t>资产覆盖率</t>
-  </si>
-  <si>
-    <t>威胁遏制率</t>
-  </si>
-  <si>
-    <t>默认100%</t>
-  </si>
-  <si>
-    <t>高危漏洞防护率</t>
-  </si>
-  <si>
-    <t>平均分析时间</t>
-  </si>
-  <si>
-    <t>平均响应时间</t>
-  </si>
-  <si>
-    <t>已闭环漏洞数量</t>
-  </si>
-  <si>
-    <t>威胁和事件数量</t>
-  </si>
-  <si>
-    <t>两名高级安全工程师成本</t>
-  </si>
-  <si>
-    <t>P27</t>
-  </si>
-  <si>
     <t>事件平均响应时间</t>
   </si>
   <si>
@@ -265,36 +267,21 @@
     <t>安全事件类型TOP5</t>
   </si>
   <si>
-    <t>渗透框架</t>
-  </si>
-  <si>
     <t>平均处置时间（分钟）</t>
   </si>
   <si>
     <t>识别</t>
   </si>
   <si>
-    <t>木马</t>
-  </si>
-  <si>
     <t>响应</t>
   </si>
   <si>
-    <t>代理工具</t>
-  </si>
-  <si>
     <t>遏制</t>
   </si>
   <si>
-    <t>挖矿</t>
-  </si>
-  <si>
     <t>处置</t>
   </si>
   <si>
-    <t>账号安全</t>
-  </si>
-  <si>
     <t>闭环</t>
   </si>
   <si>
@@ -307,7 +294,7 @@
     <t>平均响应时长</t>
   </si>
   <si>
-    <t>P28</t>
+    <t>P36</t>
   </si>
   <si>
     <t>外部攻击日志数量（XDR）</t>
@@ -346,33 +333,30 @@
     <t>安全设备策略检查次数</t>
   </si>
   <si>
+    <t>手写-安全设备策略检查次数</t>
+  </si>
+  <si>
     <t>已优化的策略风险数量</t>
   </si>
   <si>
+    <t>手写-已优化的策略风险数量</t>
+  </si>
+  <si>
     <t>最新威胁</t>
   </si>
   <si>
     <t>最新威胁情报数量</t>
   </si>
   <si>
-    <t>gpt问：帮我输出xx客户xxx时间的安全态势攻击报告</t>
-  </si>
-  <si>
     <t>最新威胁影响资产数</t>
   </si>
   <si>
     <t>威胁运营趋势---XDR平台获取</t>
   </si>
   <si>
-    <t>回到旧版，外到内</t>
-  </si>
-  <si>
     <t>外部攻击数</t>
   </si>
   <si>
-    <t>内到外，选单独月的时间取值</t>
-  </si>
-  <si>
     <t>恶意外联数</t>
   </si>
   <si>
@@ -388,7 +372,7 @@
     <t>风险主机数</t>
   </si>
   <si>
-    <t>P29</t>
+    <t>P39</t>
   </si>
   <si>
     <t>已闭环外网资产漏洞数</t>
@@ -409,6 +393,9 @@
     <t>漏洞扫描次数</t>
   </si>
   <si>
+    <t>手写-漏洞扫描次数</t>
+  </si>
+  <si>
     <t>互联网端口数量</t>
   </si>
   <si>
@@ -454,7 +441,7 @@
     <t>已闭环漏洞数</t>
   </si>
   <si>
-    <t>P30</t>
+    <t>P40</t>
   </si>
   <si>
     <t>重要时期值守次数</t>
@@ -520,6 +507,9 @@
     <t>EDR</t>
   </si>
   <si>
+    <t>不写</t>
+  </si>
+  <si>
     <t>自动处置事件数</t>
   </si>
   <si>
@@ -650,9 +640,6 @@
   </si>
   <si>
     <t>事件定性分布</t>
-  </si>
-  <si>
-    <t>处置安全事件总数</t>
   </si>
 </sst>
 </file>
@@ -869,7 +856,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -890,25 +877,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1093,7 +1068,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1163,9 +1138,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1178,7 +1151,9 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1256,17 +1231,6 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -1279,10 +1243,10 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color auto="1"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1409,7 +1373,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1421,119 +1385,119 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1570,185 +1534,206 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1756,20 +1741,26 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1777,19 +1768,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1801,7 +1792,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1">
@@ -1810,14 +1804,11 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1890,53 +1881,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1184910</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>148590</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>2164715</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>87630</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10449560" y="6734810"/>
-          <a:ext cx="979805" cy="487680"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2197,22 +2141,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N137"/>
+  <dimension ref="B1:N137"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="18.2592592592593" customWidth="1"/>
     <col min="3" max="3" width="24.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="20.6759259259259" customWidth="1"/>
+    <col min="4" max="4" width="28.8888888888889" customWidth="1"/>
     <col min="5" max="5" width="19.2314814814815" customWidth="1"/>
     <col min="6" max="6" width="28.9907407407407" customWidth="1"/>
-    <col min="7" max="7" width="14.1018518518519" customWidth="1"/>
-    <col min="8" max="8" width="39.3611111111111" customWidth="1"/>
+    <col min="7" max="8" width="20.787037037037" customWidth="1"/>
     <col min="9" max="9" width="21.4722222222222" customWidth="1"/>
     <col min="10" max="10" width="22.2685185185185" customWidth="1"/>
     <col min="11" max="11" width="20.9907407407407" customWidth="1"/>
     <col min="12" max="12" width="21.9537037037037" customWidth="1"/>
     <col min="13" max="13" width="21.4722222222222" customWidth="1"/>
-    <col min="14" max="14" width="18.5833333333333" customWidth="1"/>
+    <col min="14" max="14" width="35.5462962962963" customWidth="1"/>
     <col min="15" max="16" width="9.61111111111111"/>
     <col min="17" max="19" width="12.9259259259259"/>
     <col min="20" max="22" width="9.61111111111111"/>
@@ -2226,1115 +2169,1111 @@
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="11"/>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
+      <c r="K1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="54">
-        <f ca="1">TODAY()</f>
-        <v>46287</v>
-      </c>
-      <c r="K1" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="63"/>
-      <c r="M1" s="54"/>
+      <c r="L1" s="70"/>
+      <c r="M1" s="59"/>
     </row>
     <row r="3" spans="2:14">
       <c r="B3" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="15" t="s">
         <v>4</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>5</v>
       </c>
       <c r="E3" s="16"/>
       <c r="F3" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="17"/>
+      <c r="K3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="17"/>
-      <c r="K3" t="s">
+      <c r="L3" s="41"/>
+      <c r="N3" t="s">
         <v>7</v>
       </c>
-      <c r="N3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" ht="72" spans="2:14">
+    </row>
+    <row r="4" ht="64" customHeight="1" spans="2:14">
       <c r="B4" s="18"/>
       <c r="C4" s="19"/>
       <c r="D4" s="15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="20"/>
       <c r="F4" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="15"/>
-      <c r="N4" s="64" t="s">
+      <c r="K4" s="38" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="2:7">
+      <c r="L4" s="25"/>
+      <c r="M4" s="71"/>
+      <c r="N4" s="49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="B5" s="18"/>
       <c r="C5" s="22"/>
       <c r="D5" s="15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" s="20"/>
       <c r="F5" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="2:12">
+      <c r="L5" s="25"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="49"/>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6" s="24"/>
       <c r="C6" s="17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="20"/>
       <c r="F6" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="23"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="65"/>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="26" t="str">
+      <c r="L6" s="72"/>
+      <c r="M6" s="71"/>
+      <c r="N6" s="49"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="27" t="str">
         <f>D3</f>
         <v>手写-系统1</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="20"/>
       <c r="F7" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="23"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="65"/>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="27"/>
-      <c r="C8" s="26" t="str">
+      <c r="L7" s="72"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="49"/>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="28"/>
+      <c r="C8" s="27" t="str">
         <f>D4</f>
         <v>手写-系统2</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="20"/>
       <c r="F8" s="21" t="s">
-        <v>203</v>
+        <v>20</v>
       </c>
       <c r="G8" s="23"/>
       <c r="K8" s="4"/>
-      <c r="L8" s="65"/>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="27"/>
-      <c r="C9" s="26" t="str">
+      <c r="L8" s="72"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="49"/>
+    </row>
+    <row r="9" spans="2:14">
+      <c r="B9" s="28"/>
+      <c r="C9" s="27" t="str">
         <f>D5</f>
         <v>手写-系统3</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" s="20"/>
       <c r="F9" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="28"/>
+        <v>21</v>
+      </c>
+      <c r="G9" s="29"/>
       <c r="K9" s="4"/>
-      <c r="L9" s="65"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="2:9">
-      <c r="B10" s="29"/>
-      <c r="C10" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="31" t="s">
+      <c r="L9" s="72"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="49"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" spans="2:14">
+      <c r="B10" s="30"/>
+      <c r="C10" s="31" t="s">
         <v>22</v>
       </c>
+      <c r="D10" s="32"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="21"/>
-      <c r="I10" s="38"/>
+      <c r="G10" s="25"/>
+      <c r="I10" s="41"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="49"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="32"/>
-      <c r="C11" s="30" t="s">
+      <c r="B11" s="34"/>
+      <c r="C11" s="31" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="23"/>
-      <c r="E11" s="31"/>
+      <c r="E11" s="33"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="2:7">
-      <c r="B12" s="32"/>
-      <c r="C12" s="30" t="s">
+      <c r="B12" s="34"/>
+      <c r="C12" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="31" t="s">
+      <c r="D12" s="35"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="34"/>
+      <c r="C13" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="32"/>
-      <c r="C13" s="30" t="s">
+      <c r="D13" s="35"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="21" t="s">
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="34"/>
+      <c r="C14" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="32"/>
-      <c r="C14" s="30" t="s">
+      <c r="D14" s="35"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="21" t="s">
+      <c r="G14" s="25"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="2:7">
+      <c r="B15" s="34"/>
+      <c r="C15" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="2:7">
-      <c r="B15" s="32"/>
-      <c r="C15" s="30" t="s">
+      <c r="D15" s="35"/>
+      <c r="E15" s="33"/>
+      <c r="G15" s="36"/>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="34"/>
+      <c r="C16" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="33"/>
-    </row>
-    <row r="16" spans="2:7">
-      <c r="B16" s="32"/>
-      <c r="C16" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="23"/>
+      <c r="D16" s="35"/>
       <c r="E16" s="20"/>
       <c r="F16" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G16" s="21"/>
+        <v>33</v>
+      </c>
+      <c r="G16" s="25"/>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="32"/>
+      <c r="B17" s="34"/>
       <c r="C17" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="23"/>
+        <v>34</v>
+      </c>
+      <c r="D17" s="35"/>
       <c r="E17" s="20"/>
       <c r="F17" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="25"/>
+    </row>
+    <row r="18" ht="17" customHeight="1" spans="2:7">
+      <c r="B18" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="21"/>
-    </row>
-    <row r="18" ht="87" customHeight="1" spans="2:7">
-      <c r="B18" s="34" t="s">
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="39"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="21" t="s">
+      <c r="C20" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="21"/>
-    </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="36"/>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="37" t="s">
+      <c r="D20" s="35"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C21" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="38"/>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="39" t="s">
+      <c r="D21" s="35"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="G21" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="38"/>
-      <c r="F21" s="21" t="s">
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="42"/>
+      <c r="C22" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="41"/>
+      <c r="F22" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="38"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="39"/>
-      <c r="C22" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="21" t="s">
+      <c r="G22" s="25"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="42"/>
+      <c r="C23" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G22" s="38"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="39"/>
-      <c r="C23" s="21" t="s">
+      <c r="D23" s="43"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="25"/>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="42"/>
+      <c r="C24" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D23" s="40"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="38"/>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="39"/>
-      <c r="C24" s="21" t="s">
+      <c r="D24" s="43"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="25"/>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="44"/>
+      <c r="C25" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="40"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="38"/>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="41"/>
-      <c r="C25" s="21" t="s">
+      <c r="D25" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="45"/>
     </row>
     <row r="26" spans="2:4">
-      <c r="B26" s="36"/>
-      <c r="D26" s="42"/>
-    </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="37" t="s">
+      <c r="B26" s="39"/>
+      <c r="D26" s="46"/>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" s="40" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="15"/>
+      <c r="D27" s="35"/>
       <c r="E27" t="s">
         <v>51</v>
       </c>
-      <c r="F27" t="s">
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" s="42" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="28" spans="2:5">
-      <c r="B28" s="39" t="s">
+      <c r="C28" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="D28" s="35"/>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" s="42"/>
+      <c r="C29" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" t="s">
+      <c r="D29" s="35"/>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" s="44"/>
+      <c r="C30" s="21" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="2:5">
-      <c r="B29" s="39"/>
-      <c r="C29" s="21" t="s">
+      <c r="D30" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" t="s">
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" s="39"/>
+      <c r="D31" s="46"/>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="40" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="2:4">
-      <c r="B30" s="41"/>
-      <c r="C30" s="21" t="s">
+      <c r="C32" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="43" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4">
-      <c r="B31" s="36"/>
-      <c r="D31" s="42"/>
-    </row>
-    <row r="32" spans="2:4">
-      <c r="B32" s="37" t="s">
+      <c r="D32" s="48">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="21" t="s">
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" s="42"/>
+      <c r="C33" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="39"/>
-      <c r="C33" s="21" t="s">
+      <c r="D33" s="48">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" s="42"/>
+      <c r="C34" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D33" s="44"/>
-      <c r="E33" t="s">
+      <c r="D34" s="43"/>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" s="42"/>
+      <c r="C35" s="21" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="34" spans="2:4">
-      <c r="B34" s="39"/>
-      <c r="C34" s="21" t="s">
+      <c r="D35" s="43"/>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" s="42"/>
+      <c r="C36" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="40"/>
-    </row>
-    <row r="35" spans="2:4">
-      <c r="B35" s="39"/>
-      <c r="C35" s="21" t="s">
+      <c r="D36" s="43"/>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" s="42"/>
+      <c r="C37" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="40"/>
-    </row>
-    <row r="36" spans="2:4">
-      <c r="B36" s="39"/>
-      <c r="C36" s="21" t="s">
+      <c r="D37" s="43"/>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" s="42"/>
+      <c r="C38" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="D36" s="40"/>
-    </row>
-    <row r="37" spans="2:4">
-      <c r="B37" s="39"/>
-      <c r="C37" s="21" t="s">
+      <c r="D38" s="43"/>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" s="44"/>
+      <c r="C39" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="40"/>
-    </row>
-    <row r="38" spans="2:4">
-      <c r="B38" s="39"/>
-      <c r="C38" s="21" t="s">
+      <c r="D39" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D38" s="40"/>
-    </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="41"/>
-      <c r="C39" s="21" t="s">
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" s="39"/>
+      <c r="D40" s="46"/>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" s="39"/>
+      <c r="D41" s="46"/>
+    </row>
+    <row r="42" spans="2:4">
+      <c r="B42" s="39"/>
+      <c r="D42" s="46"/>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" s="39"/>
+      <c r="D43" s="46"/>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" s="39"/>
+      <c r="D44" s="46"/>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" s="39"/>
+      <c r="D45" s="46"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="39"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="49"/>
+    </row>
+    <row r="48" spans="2:14">
+      <c r="B48" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4">
-      <c r="B40" s="36"/>
-      <c r="D40" s="42"/>
-    </row>
-    <row r="41" spans="2:4">
-      <c r="B41" s="36"/>
-      <c r="D41" s="42"/>
-    </row>
-    <row r="42" spans="2:4">
-      <c r="B42" s="36"/>
-      <c r="D42" s="42"/>
-    </row>
-    <row r="43" spans="2:4">
-      <c r="B43" s="36"/>
-      <c r="D43" s="42"/>
-    </row>
-    <row r="44" spans="2:4">
-      <c r="B44" s="36"/>
-      <c r="D44" s="42"/>
-    </row>
-    <row r="45" spans="2:4">
-      <c r="B45" s="36"/>
-      <c r="D45" s="42"/>
-    </row>
-    <row r="46" spans="2:2">
-      <c r="B46" s="36"/>
-    </row>
-    <row r="47" spans="2:2">
-      <c r="B47" s="45"/>
-    </row>
-    <row r="48" spans="2:14">
-      <c r="B48" s="12" t="s">
+      <c r="C48" s="23" t="s">
         <v>69</v>
-      </c>
-      <c r="C48" s="23" t="s">
-        <v>19</v>
       </c>
       <c r="D48" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="E48" s="21" t="s">
+      <c r="E48" s="25" t="s">
         <v>71</v>
       </c>
       <c r="F48" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="G48" s="46"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="46"/>
-      <c r="L48" s="46"/>
-      <c r="M48" s="46"/>
-      <c r="N48" s="66"/>
+      <c r="G48" s="51"/>
+      <c r="H48" s="51"/>
+      <c r="I48" s="51"/>
+      <c r="J48" s="51"/>
+      <c r="K48" s="51"/>
+      <c r="L48" s="51"/>
+      <c r="M48" s="51"/>
+      <c r="N48" s="74"/>
     </row>
     <row r="49" spans="2:14">
-      <c r="B49" s="12"/>
+      <c r="B49" s="50"/>
       <c r="C49" s="23"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="48"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
-      <c r="N49" s="33"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="41"/>
+      <c r="N49" s="36"/>
     </row>
     <row r="50" spans="2:14">
-      <c r="B50" s="49"/>
-      <c r="H50" s="20"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="38"/>
-      <c r="L50" s="38"/>
-      <c r="M50" s="38"/>
-      <c r="N50" s="33"/>
+      <c r="B50" s="54"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="41"/>
+      <c r="L50" s="41"/>
+      <c r="M50" s="41"/>
+      <c r="N50" s="36"/>
     </row>
     <row r="51" spans="2:14">
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="50" t="s">
+      <c r="C51" s="55"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="D51" s="23"/>
-      <c r="E51" s="12" t="s">
+      <c r="F51" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="F51" s="23" t="s">
+      <c r="G51" s="56"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="41"/>
+      <c r="J51" s="41"/>
+      <c r="K51" s="41"/>
+      <c r="L51" s="41"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="36"/>
+    </row>
+    <row r="52" spans="2:14">
+      <c r="B52" s="50"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="G51" s="51"/>
-      <c r="H51" s="20"/>
-      <c r="I51" s="38"/>
-      <c r="J51" s="38"/>
-      <c r="K51" s="38"/>
-      <c r="L51" s="38"/>
-      <c r="M51" s="38"/>
-      <c r="N51" s="33"/>
-    </row>
-    <row r="52" spans="2:14">
-      <c r="B52" s="12"/>
-      <c r="C52" s="52" t="s">
+      <c r="G52" s="56"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="41"/>
+      <c r="J52" s="41"/>
+      <c r="K52" s="41"/>
+      <c r="L52" s="41"/>
+      <c r="M52" s="41"/>
+      <c r="N52" s="36"/>
+    </row>
+    <row r="53" spans="2:14">
+      <c r="B53" s="50"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="50"/>
+      <c r="F53" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="23"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="23" t="s">
+      <c r="G53" s="56"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="41"/>
+      <c r="J53" s="41"/>
+      <c r="K53" s="41"/>
+      <c r="L53" s="41"/>
+      <c r="M53" s="41"/>
+      <c r="N53" s="36"/>
+    </row>
+    <row r="54" spans="2:14">
+      <c r="B54" s="50"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="50"/>
+      <c r="F54" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="G52" s="51"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="38"/>
-      <c r="L52" s="38"/>
-      <c r="M52" s="38"/>
-      <c r="N52" s="33"/>
-    </row>
-    <row r="53" spans="2:14">
-      <c r="B53" s="12"/>
-      <c r="C53" s="52" t="s">
+      <c r="G54" s="56"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="41"/>
+      <c r="J54" s="41"/>
+      <c r="K54" s="41"/>
+      <c r="L54" s="41"/>
+      <c r="M54" s="41"/>
+      <c r="N54" s="36"/>
+    </row>
+    <row r="55" spans="2:14">
+      <c r="B55" s="50"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="50"/>
+      <c r="F55" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="D53" s="23"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="G53" s="51"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="38"/>
-      <c r="L53" s="38"/>
-      <c r="M53" s="38"/>
-      <c r="N53" s="33"/>
-    </row>
-    <row r="54" spans="2:14">
-      <c r="B54" s="12"/>
-      <c r="C54" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" s="23"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="G54" s="51"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="33"/>
-    </row>
-    <row r="55" spans="2:14">
-      <c r="B55" s="12"/>
-      <c r="C55" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="D55" s="23"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="G55" s="51"/>
+      <c r="G55" s="56"/>
       <c r="H55" s="20"/>
-      <c r="I55" s="38"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="38"/>
-      <c r="L55" s="38"/>
-      <c r="M55" s="38"/>
-      <c r="N55" s="33"/>
+      <c r="I55" s="41"/>
+      <c r="J55" s="41"/>
+      <c r="K55" s="41"/>
+      <c r="L55" s="41"/>
+      <c r="M55" s="41"/>
+      <c r="N55" s="36"/>
     </row>
     <row r="56" spans="2:14">
-      <c r="B56" s="49"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="38"/>
-      <c r="L56" s="38"/>
-      <c r="M56" s="38"/>
-      <c r="N56" s="33"/>
+      <c r="B56" s="54"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
+      <c r="J56" s="41"/>
+      <c r="K56" s="41"/>
+      <c r="L56" s="41"/>
+      <c r="M56" s="41"/>
+      <c r="N56" s="36"/>
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="67"/>
-      <c r="J57" s="67"/>
-      <c r="K57" s="67"/>
-      <c r="L57" s="67"/>
-      <c r="M57" s="67"/>
-      <c r="N57" s="68"/>
+        <v>80</v>
+      </c>
+      <c r="C57" s="41"/>
+      <c r="D57" s="41"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="58"/>
+      <c r="I57" s="58"/>
+      <c r="J57" s="58"/>
+      <c r="K57" s="58"/>
+      <c r="L57" s="58"/>
+      <c r="M57" s="58"/>
+      <c r="N57" s="36"/>
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="21" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C58" s="23"/>
-      <c r="D58" s="54"/>
-      <c r="E58" s="54"/>
-      <c r="F58" s="54"/>
-      <c r="G58" s="54"/>
-      <c r="H58" s="55"/>
-      <c r="I58" s="55"/>
-      <c r="J58" s="55"/>
-      <c r="K58" s="55"/>
-      <c r="L58" s="55"/>
-      <c r="M58" s="55"/>
-      <c r="N58" s="55"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="60"/>
+      <c r="J58" s="60"/>
+      <c r="K58" s="60"/>
+      <c r="L58" s="60"/>
+      <c r="M58" s="60"/>
+      <c r="N58" s="59"/>
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="47"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="47"/>
-      <c r="G59" s="47"/>
-      <c r="H59" s="47"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
-      <c r="L59" s="47"/>
-      <c r="M59" s="47"/>
-      <c r="N59" s="47"/>
+        <v>82</v>
+      </c>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59" s="52"/>
     </row>
     <row r="60" spans="2:2">
-      <c r="B60" s="45"/>
+      <c r="B60" s="49"/>
     </row>
     <row r="61" ht="30" customHeight="1" spans="2:14">
       <c r="B61" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" s="61"/>
+      <c r="E61" s="51"/>
+      <c r="F61" s="62" t="s">
+        <v>85</v>
+      </c>
+      <c r="G61" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="H61" s="64"/>
+      <c r="I61" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="J61" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="K61" s="64"/>
+      <c r="L61" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="C61" s="21" t="s">
+      <c r="M61" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="D61" s="56"/>
-      <c r="E61" s="46"/>
-      <c r="F61" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="G61" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="H61" s="59"/>
-      <c r="I61" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="J61" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="K61" s="59"/>
-      <c r="L61" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="M61" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="N61" s="66"/>
+      <c r="N61" s="74"/>
     </row>
     <row r="62" ht="27" customHeight="1" spans="2:14">
       <c r="B62" s="23" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" s="23"/>
-      <c r="F62" s="60"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="62"/>
-      <c r="I62" s="60"/>
-      <c r="J62" s="61"/>
-      <c r="K62" s="62"/>
-      <c r="L62" s="70"/>
-      <c r="M62" s="71"/>
-      <c r="N62" s="33"/>
+        <v>91</v>
+      </c>
+      <c r="D62" s="35"/>
+      <c r="F62" s="65"/>
+      <c r="G62" s="66"/>
+      <c r="H62" s="67"/>
+      <c r="I62" s="65"/>
+      <c r="J62" s="66"/>
+      <c r="K62" s="67"/>
+      <c r="L62" s="76"/>
+      <c r="M62" s="77"/>
+      <c r="N62" s="36"/>
     </row>
     <row r="63" ht="27" customHeight="1" spans="2:14">
       <c r="B63" s="23"/>
       <c r="C63" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D63" s="23"/>
-      <c r="F63" s="60"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="62"/>
-      <c r="I63" s="60"/>
-      <c r="J63" s="61"/>
-      <c r="K63" s="62"/>
-      <c r="L63" s="70"/>
-      <c r="M63" s="71"/>
-      <c r="N63" s="33"/>
+        <v>92</v>
+      </c>
+      <c r="D63" s="35"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="67"/>
+      <c r="I63" s="65"/>
+      <c r="J63" s="66"/>
+      <c r="K63" s="67"/>
+      <c r="L63" s="76"/>
+      <c r="M63" s="77"/>
+      <c r="N63" s="36"/>
     </row>
     <row r="64" ht="27" customHeight="1" spans="2:14">
       <c r="B64" s="23"/>
       <c r="C64" s="21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D64" s="23"/>
-      <c r="F64" s="60"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="62"/>
-      <c r="I64" s="60"/>
-      <c r="J64" s="61"/>
-      <c r="K64" s="62"/>
-      <c r="L64" s="70"/>
-      <c r="M64" s="71"/>
-      <c r="N64" s="33"/>
+        <v>93</v>
+      </c>
+      <c r="D64" s="35"/>
+      <c r="F64" s="65"/>
+      <c r="G64" s="66"/>
+      <c r="H64" s="67"/>
+      <c r="I64" s="65"/>
+      <c r="J64" s="66"/>
+      <c r="K64" s="67"/>
+      <c r="L64" s="76"/>
+      <c r="M64" s="77"/>
+      <c r="N64" s="36"/>
     </row>
     <row r="65" ht="27" customHeight="1" spans="2:14">
       <c r="B65" s="23" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="D65" s="15"/>
-      <c r="F65" s="60"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="62"/>
-      <c r="I65" s="57"/>
-      <c r="J65" s="58"/>
-      <c r="K65" s="62"/>
-      <c r="L65" s="70"/>
-      <c r="M65" s="71"/>
-      <c r="N65" s="33"/>
+        <v>95</v>
+      </c>
+      <c r="D65" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="F65" s="65"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="67"/>
+      <c r="I65" s="62"/>
+      <c r="J65" s="63"/>
+      <c r="K65" s="67"/>
+      <c r="L65" s="76"/>
+      <c r="M65" s="77"/>
+      <c r="N65" s="36"/>
     </row>
     <row r="66" ht="27" customHeight="1" spans="2:14">
       <c r="B66" s="23"/>
       <c r="C66" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D66" s="15"/>
-      <c r="F66" s="60"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="62"/>
-      <c r="I66" s="60"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="62"/>
-      <c r="L66" s="70"/>
-      <c r="M66" s="71"/>
-      <c r="N66" s="33"/>
+        <v>97</v>
+      </c>
+      <c r="D66" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="F66" s="65"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="67"/>
+      <c r="I66" s="65"/>
+      <c r="J66" s="66"/>
+      <c r="K66" s="67"/>
+      <c r="L66" s="76"/>
+      <c r="M66" s="77"/>
+      <c r="N66" s="36"/>
     </row>
     <row r="67" ht="27" customHeight="1" spans="2:14">
       <c r="B67" s="23" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D67" s="23"/>
-      <c r="F67" t="s">
-        <v>104</v>
-      </c>
-      <c r="N67" s="33"/>
+        <v>100</v>
+      </c>
+      <c r="D67" s="35"/>
+      <c r="N67" s="36"/>
     </row>
     <row r="68" ht="27" customHeight="1" spans="2:14">
       <c r="B68" s="23"/>
       <c r="C68" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68" s="15"/>
-      <c r="N68" s="33"/>
+        <v>101</v>
+      </c>
+      <c r="D68" s="35"/>
+      <c r="N68" s="36"/>
     </row>
     <row r="69" spans="2:14">
       <c r="B69" s="20"/>
-      <c r="N69" s="33"/>
+      <c r="N69" s="36"/>
     </row>
     <row r="70" spans="2:14">
-      <c r="B70" s="72" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" s="73"/>
-      <c r="D70" s="73"/>
-      <c r="E70" s="73"/>
-      <c r="F70" s="73"/>
-      <c r="G70" s="73"/>
-      <c r="H70" s="73"/>
-      <c r="I70" s="73"/>
-      <c r="J70" s="73"/>
-      <c r="K70" s="73"/>
-      <c r="L70" s="73"/>
-      <c r="M70" s="73"/>
-      <c r="N70" s="91"/>
+      <c r="B70" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="C70" s="80"/>
+      <c r="D70" s="80"/>
+      <c r="E70" s="80"/>
+      <c r="F70" s="80"/>
+      <c r="G70" s="80"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="80"/>
+      <c r="J70" s="80"/>
+      <c r="K70" s="80"/>
+      <c r="L70" s="80"/>
+      <c r="M70" s="80"/>
+      <c r="N70" s="101"/>
     </row>
     <row r="71" spans="2:14">
       <c r="B71" s="23"/>
       <c r="C71" s="23"/>
-      <c r="D71" s="54"/>
-      <c r="E71" s="54"/>
-      <c r="F71" s="54"/>
-      <c r="G71" s="54"/>
-      <c r="H71" s="54"/>
-      <c r="I71" s="54"/>
-      <c r="J71" s="54"/>
-      <c r="K71" s="54"/>
-      <c r="L71" s="54"/>
-      <c r="M71" s="54"/>
-      <c r="N71" s="54"/>
-    </row>
-    <row r="72" spans="1:14">
-      <c r="A72" t="s">
-        <v>107</v>
-      </c>
+      <c r="D71" s="59"/>
+      <c r="E71" s="59"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="59"/>
+      <c r="H71" s="59"/>
+      <c r="I71" s="59"/>
+      <c r="J71" s="59"/>
+      <c r="K71" s="59"/>
+      <c r="L71" s="59"/>
+      <c r="M71" s="59"/>
+      <c r="N71" s="59"/>
+    </row>
+    <row r="72" spans="2:14">
       <c r="B72" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C72" s="56"/>
-      <c r="D72" s="56"/>
-      <c r="E72" s="56"/>
-      <c r="F72" s="56"/>
-      <c r="G72" s="56"/>
-      <c r="H72" s="56"/>
-      <c r="I72" s="56"/>
-      <c r="J72" s="56"/>
-      <c r="K72" s="56"/>
-      <c r="L72" s="56"/>
-      <c r="M72" s="56"/>
-      <c r="N72" s="56"/>
-    </row>
-    <row r="73" spans="1:14">
-      <c r="A73" t="s">
-        <v>109</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C72" s="81"/>
+      <c r="D72" s="81"/>
+      <c r="E72" s="81"/>
+      <c r="F72" s="81"/>
+      <c r="G72" s="81"/>
+      <c r="H72" s="81"/>
+      <c r="I72" s="81"/>
+      <c r="J72" s="81"/>
+      <c r="K72" s="81"/>
+      <c r="L72" s="81"/>
+      <c r="M72" s="81"/>
+      <c r="N72" s="81"/>
+    </row>
+    <row r="73" spans="2:14">
       <c r="B73" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C73" s="56"/>
-      <c r="D73" s="56"/>
-      <c r="E73" s="56"/>
-      <c r="F73" s="56"/>
-      <c r="G73" s="56"/>
-      <c r="H73" s="56"/>
-      <c r="I73" s="56"/>
-      <c r="J73" s="56"/>
-      <c r="K73" s="56"/>
-      <c r="L73" s="56"/>
-      <c r="M73" s="56"/>
-      <c r="N73" s="56"/>
+        <v>104</v>
+      </c>
+      <c r="C73" s="81"/>
+      <c r="D73" s="81"/>
+      <c r="E73" s="81"/>
+      <c r="F73" s="81"/>
+      <c r="G73" s="81"/>
+      <c r="H73" s="81"/>
+      <c r="I73" s="81"/>
+      <c r="J73" s="81"/>
+      <c r="K73" s="81"/>
+      <c r="L73" s="81"/>
+      <c r="M73" s="81"/>
+      <c r="N73" s="81"/>
     </row>
     <row r="74" spans="2:14">
       <c r="B74" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="C74" s="56"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="56"/>
-      <c r="F74" s="56"/>
-      <c r="G74" s="56"/>
-      <c r="H74" s="56"/>
-      <c r="I74" s="56"/>
-      <c r="J74" s="56"/>
-      <c r="K74" s="56"/>
-      <c r="L74" s="56"/>
-      <c r="M74" s="56"/>
-      <c r="N74" s="56"/>
+        <v>105</v>
+      </c>
+      <c r="C74" s="81"/>
+      <c r="D74" s="81"/>
+      <c r="E74" s="81"/>
+      <c r="F74" s="81"/>
+      <c r="G74" s="81"/>
+      <c r="H74" s="81"/>
+      <c r="I74" s="81"/>
+      <c r="J74" s="81"/>
+      <c r="K74" s="81"/>
+      <c r="L74" s="81"/>
+      <c r="M74" s="81"/>
+      <c r="N74" s="81"/>
     </row>
     <row r="75" spans="2:14">
       <c r="B75" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C75" s="23"/>
-      <c r="D75" s="23"/>
-      <c r="E75" s="23"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="23"/>
-      <c r="K75" s="23"/>
-      <c r="L75" s="23"/>
-      <c r="M75" s="23"/>
-      <c r="N75" s="23"/>
+        <v>106</v>
+      </c>
+      <c r="C75" s="35"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
+      <c r="L75" s="35"/>
+      <c r="M75" s="35"/>
+      <c r="N75" s="35"/>
     </row>
     <row r="76" spans="2:14">
       <c r="B76" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="23"/>
-      <c r="N76" s="23"/>
+        <v>107</v>
+      </c>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="35"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35"/>
+      <c r="I76" s="35"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="35"/>
+      <c r="L76" s="35"/>
+      <c r="M76" s="35"/>
+      <c r="N76" s="35"/>
     </row>
     <row r="77" spans="2:14">
       <c r="B77" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
-      <c r="M77" s="15"/>
-      <c r="N77" s="15"/>
+        <v>108</v>
+      </c>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="35"/>
+      <c r="J77" s="35"/>
+      <c r="K77" s="35"/>
+      <c r="L77" s="35"/>
+      <c r="M77" s="35"/>
+      <c r="N77" s="35"/>
     </row>
     <row r="78" spans="3:3">
-      <c r="C78" s="74"/>
+      <c r="C78" s="82"/>
     </row>
     <row r="79" ht="24" customHeight="1" spans="2:14">
       <c r="B79" s="23" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>116</v>
+        <v>22</v>
+      </c>
+      <c r="D79" s="50" t="s">
+        <v>110</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G79" s="46"/>
+        <v>112</v>
+      </c>
+      <c r="G79" s="51"/>
       <c r="H79" s="21" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="I79" s="23"/>
       <c r="J79" s="21" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="K79" s="23"/>
-      <c r="L79" s="46"/>
+      <c r="L79" s="51"/>
       <c r="M79" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="N79" s="78"/>
+        <v>115</v>
+      </c>
+      <c r="N79" s="15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="80" spans="2:14">
       <c r="B80" s="23"/>
       <c r="C80" s="23"/>
       <c r="D80" s="23"/>
-      <c r="E80" s="75"/>
-      <c r="F80" s="48"/>
+      <c r="E80" s="35"/>
+      <c r="F80" s="53"/>
       <c r="H80" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="I80" s="23"/>
+        <v>117</v>
+      </c>
+      <c r="I80" s="35"/>
       <c r="J80" s="21" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K80" s="23"/>
-      <c r="N80" s="33"/>
+      <c r="N80" s="36"/>
     </row>
     <row r="81" spans="2:14">
-      <c r="B81" s="76"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="38"/>
-      <c r="F81" s="38"/>
+      <c r="B81" s="83"/>
+      <c r="C81" s="41"/>
+      <c r="D81" s="41"/>
+      <c r="E81" s="41"/>
+      <c r="F81" s="41"/>
       <c r="H81" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="I81" s="15"/>
+        <v>119</v>
+      </c>
+      <c r="I81" s="35"/>
       <c r="J81" s="21" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K81" s="23"/>
-      <c r="N81" s="33"/>
+      <c r="N81" s="36"/>
     </row>
     <row r="82" spans="2:14">
       <c r="B82" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C82" s="77"/>
+        <v>121</v>
+      </c>
+      <c r="C82" s="84"/>
       <c r="D82" s="23" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H82" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="I82" s="23"/>
+        <v>125</v>
+      </c>
+      <c r="I82" s="35"/>
       <c r="J82" s="21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K82" s="23"/>
-      <c r="N82" s="33"/>
+      <c r="N82" s="36"/>
     </row>
     <row r="83" spans="2:14">
       <c r="B83" s="23"/>
       <c r="C83" s="21" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D83" s="23"/>
       <c r="E83" s="23"/>
-      <c r="F83" s="48"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="21"/>
+      <c r="F83" s="53"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="74"/>
       <c r="J83" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K83" s="23"/>
-      <c r="N83" s="33"/>
+      <c r="N83" s="36"/>
     </row>
     <row r="84" spans="2:14">
       <c r="B84" s="23"/>
       <c r="C84" s="21" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D84" s="23"/>
       <c r="E84" s="23"/>
-      <c r="F84" s="48"/>
-      <c r="N84" s="33"/>
+      <c r="F84" s="53"/>
+      <c r="H84" s="85"/>
+      <c r="I84" s="85"/>
+      <c r="N84" s="36"/>
     </row>
     <row r="85" spans="2:14">
       <c r="B85" s="23"/>
       <c r="C85" s="21" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D85" s="23"/>
       <c r="E85" s="23"/>
-      <c r="F85" s="48"/>
-      <c r="N85" s="33"/>
+      <c r="F85" s="53"/>
+      <c r="N85" s="36"/>
     </row>
     <row r="86" spans="2:14">
       <c r="B86" s="23" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C86" s="23"/>
-      <c r="D86" s="54"/>
-      <c r="E86" s="54"/>
-      <c r="F86" s="54"/>
-      <c r="G86" s="54"/>
-      <c r="H86" s="54"/>
-      <c r="I86" s="54"/>
-      <c r="J86" s="54"/>
-      <c r="K86" s="54"/>
-      <c r="L86" s="54"/>
-      <c r="M86" s="54"/>
-      <c r="N86" s="54"/>
+      <c r="D86" s="59"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="59"/>
+      <c r="I86" s="59"/>
+      <c r="J86" s="59"/>
+      <c r="K86" s="59"/>
+      <c r="L86" s="59"/>
+      <c r="M86" s="59"/>
+      <c r="N86" s="59"/>
     </row>
     <row r="87" spans="2:14">
       <c r="B87" s="23" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C87" s="23"/>
       <c r="D87" s="23"/>
@@ -3351,7 +3290,7 @@
     </row>
     <row r="88" spans="2:14">
       <c r="B88" s="23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C88" s="23"/>
       <c r="D88" s="23"/>
@@ -3368,490 +3307,525 @@
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="16" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="D90" s="15"/>
-      <c r="E90" s="25" t="s">
-        <v>139</v>
+        <v>133</v>
+      </c>
+      <c r="D90" s="35"/>
+      <c r="E90" s="26" t="s">
+        <v>134</v>
       </c>
       <c r="F90" s="21"/>
       <c r="G90" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H90" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="D91" s="15"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="78"/>
-      <c r="G91" s="56"/>
-      <c r="H91" s="44"/>
+        <v>138</v>
+      </c>
+      <c r="D91" s="35"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="86"/>
+      <c r="G91" s="81"/>
+      <c r="H91" s="87"/>
     </row>
     <row r="92" spans="2:8">
-      <c r="B92" s="79"/>
+      <c r="B92" s="88"/>
       <c r="C92" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="D92" s="44"/>
-      <c r="E92" s="27"/>
-      <c r="F92" s="78"/>
-      <c r="G92" s="56"/>
-      <c r="H92" s="44"/>
+        <v>139</v>
+      </c>
+      <c r="D92" s="48">
+        <v>1</v>
+      </c>
+      <c r="E92" s="28"/>
+      <c r="F92" s="86"/>
+      <c r="G92" s="81"/>
+      <c r="H92" s="87"/>
     </row>
     <row r="93" spans="2:8">
       <c r="B93" s="20"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="80"/>
-      <c r="E93" s="27"/>
-      <c r="F93" s="78"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="44"/>
+      <c r="C93" s="41"/>
+      <c r="D93" s="89"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="86"/>
+      <c r="G93" s="81"/>
+      <c r="H93" s="87"/>
     </row>
     <row r="94" spans="2:8">
       <c r="B94" s="20"/>
-      <c r="C94" s="38"/>
-      <c r="D94" s="80"/>
-      <c r="E94" s="27"/>
-      <c r="F94" s="78"/>
-      <c r="G94" s="56"/>
-      <c r="H94" s="44"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="89"/>
+      <c r="E94" s="28"/>
+      <c r="F94" s="86"/>
+      <c r="G94" s="81"/>
+      <c r="H94" s="87"/>
     </row>
     <row r="95" spans="2:8">
       <c r="B95" s="20"/>
-      <c r="C95" s="38"/>
-      <c r="D95" s="80"/>
-      <c r="E95" s="27"/>
-      <c r="F95" s="78"/>
-      <c r="G95" s="15"/>
-      <c r="H95" s="44"/>
+      <c r="C95" s="41"/>
+      <c r="D95" s="89"/>
+      <c r="E95" s="28"/>
+      <c r="F95" s="86"/>
+      <c r="G95" s="81"/>
+      <c r="H95" s="87"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="20"/>
-      <c r="C96" s="38"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="27"/>
-      <c r="F96" s="78"/>
-      <c r="G96" s="15"/>
-      <c r="H96" s="44"/>
+      <c r="C96" s="41"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="28"/>
+      <c r="F96" s="86"/>
+      <c r="G96" s="81"/>
+      <c r="H96" s="87"/>
     </row>
     <row r="97" spans="2:8">
-      <c r="B97" s="53"/>
-      <c r="C97" s="81"/>
-      <c r="D97" s="67"/>
-      <c r="E97" s="82"/>
-      <c r="F97" s="78"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="44"/>
+      <c r="B97" s="90"/>
+      <c r="C97" s="91"/>
+      <c r="D97" s="58"/>
+      <c r="E97" s="92"/>
+      <c r="F97" s="86"/>
+      <c r="G97" s="81"/>
+      <c r="H97" s="87"/>
     </row>
     <row r="99" spans="2:8">
-      <c r="B99" s="35" t="s">
-        <v>145</v>
+      <c r="B99" s="38" t="s">
+        <v>140</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="D99" s="21"/>
-      <c r="F99" t="s">
-        <v>147</v>
-      </c>
-      <c r="G99" s="83"/>
-      <c r="H99" s="66"/>
+        <v>141</v>
+      </c>
+      <c r="D99" s="25"/>
+      <c r="F99" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="G99" s="25"/>
+      <c r="H99" s="41"/>
     </row>
     <row r="100" spans="2:8">
       <c r="B100" s="20"/>
       <c r="C100" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D100" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="F100" s="84" t="s">
-        <v>149</v>
-      </c>
-      <c r="G100" s="83"/>
-      <c r="H100" s="33"/>
+        <v>143</v>
+      </c>
+      <c r="D100" s="25"/>
+      <c r="F100" s="93" t="s">
+        <v>144</v>
+      </c>
+      <c r="G100" s="25"/>
+      <c r="H100" s="41"/>
     </row>
     <row r="101" spans="2:8">
       <c r="B101" s="20"/>
       <c r="C101" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="D101" s="83"/>
-      <c r="F101" s="84" t="s">
-        <v>151</v>
-      </c>
-      <c r="G101" s="83"/>
-      <c r="H101" s="33"/>
+        <v>145</v>
+      </c>
+      <c r="D101" s="25"/>
+      <c r="F101" s="93" t="s">
+        <v>146</v>
+      </c>
+      <c r="G101" s="25"/>
+      <c r="H101" s="41"/>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="20"/>
       <c r="C102" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="D102" s="83"/>
-      <c r="F102" s="84" t="s">
-        <v>153</v>
-      </c>
-      <c r="G102" s="83"/>
-      <c r="H102" s="33"/>
+        <v>147</v>
+      </c>
+      <c r="D102" s="25"/>
+      <c r="F102" s="93" t="s">
+        <v>148</v>
+      </c>
+      <c r="G102" s="25"/>
+      <c r="H102" s="41"/>
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="20"/>
       <c r="C103" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="D103" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="F103" s="84" t="s">
-        <v>155</v>
-      </c>
-      <c r="G103" s="83"/>
-      <c r="H103" s="33"/>
+        <v>149</v>
+      </c>
+      <c r="D103" s="25"/>
+      <c r="F103" s="93" t="s">
+        <v>150</v>
+      </c>
+      <c r="G103" s="25"/>
+      <c r="H103" s="41"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="20"/>
       <c r="C104" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D104" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="F104" s="84" t="s">
-        <v>157</v>
-      </c>
-      <c r="G104" s="83"/>
-      <c r="H104" s="33"/>
-    </row>
-    <row r="105" spans="2:7">
+        <v>151</v>
+      </c>
+      <c r="D104" s="25"/>
+      <c r="F104" s="93" t="s">
+        <v>152</v>
+      </c>
+      <c r="G104" s="25"/>
+      <c r="H104" s="41"/>
+    </row>
+    <row r="105" spans="2:8">
       <c r="B105" s="20"/>
       <c r="C105" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="D105" s="83"/>
-      <c r="F105" s="84" t="s">
-        <v>159</v>
-      </c>
-      <c r="G105" s="83"/>
+        <v>153</v>
+      </c>
+      <c r="D105" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="F105" s="93" t="s">
+        <v>155</v>
+      </c>
+      <c r="G105" s="25"/>
+      <c r="H105" s="85"/>
     </row>
     <row r="106" spans="2:8">
-      <c r="B106" s="53"/>
+      <c r="B106" s="90"/>
       <c r="C106" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="D106" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="D106" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E106" s="67"/>
-      <c r="F106" s="84" t="s">
-        <v>160</v>
-      </c>
-      <c r="G106" s="83"/>
-      <c r="H106" s="33"/>
+      <c r="E106" s="58"/>
+      <c r="F106" s="93" t="s">
+        <v>156</v>
+      </c>
+      <c r="G106" s="25"/>
+      <c r="H106" s="41"/>
     </row>
     <row r="107" spans="2:8">
-      <c r="B107" s="53"/>
-      <c r="C107" s="67"/>
-      <c r="D107" s="85"/>
-      <c r="E107" s="67"/>
-      <c r="F107" s="84" t="s">
-        <v>161</v>
-      </c>
-      <c r="G107" s="83"/>
-      <c r="H107" s="68"/>
+      <c r="B107" s="90"/>
+      <c r="C107" s="58"/>
+      <c r="D107" s="94"/>
+      <c r="E107" s="58"/>
+      <c r="F107" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="G107" s="25"/>
+      <c r="H107" s="41"/>
     </row>
     <row r="108" spans="6:6">
-      <c r="F108" s="86"/>
+      <c r="F108" s="95"/>
     </row>
     <row r="109" spans="2:8">
       <c r="B109" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="C109" s="51"/>
+      <c r="D109" s="51"/>
+      <c r="E109" s="51"/>
+      <c r="F109" s="96"/>
+      <c r="G109" s="25"/>
+      <c r="H109" s="41"/>
+    </row>
+    <row r="110" spans="2:8">
+      <c r="B110" s="30"/>
+      <c r="C110" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="D110" s="25"/>
+      <c r="F110" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="G110" s="25"/>
+      <c r="H110" s="85"/>
+    </row>
+    <row r="111" spans="2:8">
+      <c r="B111" s="34"/>
+      <c r="C111" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="D111" s="25"/>
+      <c r="F111" s="98" t="s">
         <v>162</v>
       </c>
-      <c r="C109" s="46"/>
-      <c r="D109" s="46"/>
-      <c r="E109" s="46"/>
-      <c r="F109" s="87"/>
-      <c r="G109" s="46"/>
-      <c r="H109" s="66"/>
-    </row>
-    <row r="110" spans="2:7">
-      <c r="B110" s="29"/>
-      <c r="C110" s="88" t="s">
+      <c r="G111" s="25"/>
+      <c r="H111" s="41"/>
+    </row>
+    <row r="112" spans="2:8">
+      <c r="B112" s="34"/>
+      <c r="C112" s="97" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" s="25"/>
+      <c r="F112" s="98" t="s">
         <v>163</v>
       </c>
-      <c r="D110" s="21"/>
-      <c r="F110" s="21" t="s">
+      <c r="G112" s="25"/>
+      <c r="H112" s="41"/>
+    </row>
+    <row r="113" spans="2:8">
+      <c r="B113" s="34"/>
+      <c r="C113" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="G110" s="21"/>
-    </row>
-    <row r="111" spans="2:8">
-      <c r="B111" s="32"/>
-      <c r="C111" s="88" t="s">
+      <c r="D113" s="25"/>
+      <c r="F113" s="98" t="s">
         <v>165</v>
       </c>
-      <c r="D111" s="21"/>
-      <c r="F111" s="89" t="s">
+      <c r="G113" s="25"/>
+      <c r="H113" s="41"/>
+    </row>
+    <row r="114" spans="2:8">
+      <c r="B114" s="34"/>
+      <c r="C114" s="99" t="s">
         <v>166</v>
       </c>
-      <c r="G111" s="21"/>
-      <c r="H111" s="33"/>
-    </row>
-    <row r="112" spans="2:8">
-      <c r="B112" s="32"/>
-      <c r="C112" s="88" t="s">
-        <v>24</v>
-      </c>
-      <c r="D112" s="21"/>
-      <c r="F112" s="89" t="s">
+      <c r="D114" s="25"/>
+      <c r="F114" s="98" t="s">
         <v>167</v>
       </c>
-      <c r="G112" s="21"/>
-      <c r="H112" s="33"/>
-    </row>
-    <row r="113" spans="2:8">
-      <c r="B113" s="32"/>
-      <c r="C113" s="88" t="s">
+      <c r="G114" s="25"/>
+      <c r="H114" s="41"/>
+    </row>
+    <row r="115" spans="2:8">
+      <c r="B115" s="34"/>
+      <c r="C115" s="99" t="s">
+        <v>160</v>
+      </c>
+      <c r="D115" s="25"/>
+      <c r="F115" s="98" t="s">
         <v>168</v>
       </c>
-      <c r="D113" s="21"/>
-      <c r="F113" s="89" t="s">
+      <c r="G115" s="25"/>
+      <c r="H115" s="41"/>
+    </row>
+    <row r="116" spans="2:8">
+      <c r="B116" s="34"/>
+      <c r="C116" s="99" t="s">
+        <v>29</v>
+      </c>
+      <c r="D116" s="25"/>
+      <c r="F116" s="98" t="s">
         <v>169</v>
       </c>
-      <c r="G113" s="21"/>
-      <c r="H113" s="33"/>
-    </row>
-    <row r="114" spans="2:8">
-      <c r="B114" s="32"/>
-      <c r="C114" s="89" t="s">
+      <c r="G116" s="25"/>
+      <c r="H116" s="41"/>
+    </row>
+    <row r="117" spans="2:8">
+      <c r="B117" s="34"/>
+      <c r="C117" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="D117" s="25"/>
+      <c r="F117" s="98" t="s">
         <v>170</v>
       </c>
-      <c r="D114" s="21"/>
-      <c r="F114" s="89" t="s">
+      <c r="G117" s="25"/>
+      <c r="H117" s="41"/>
+    </row>
+    <row r="118" spans="2:8">
+      <c r="B118" s="34"/>
+      <c r="C118" s="99" t="s">
         <v>171</v>
       </c>
-      <c r="G114" s="21"/>
-      <c r="H114" s="33"/>
-    </row>
-    <row r="115" spans="2:8">
-      <c r="B115" s="32"/>
-      <c r="C115" s="89" t="s">
-        <v>164</v>
-      </c>
-      <c r="D115" s="21"/>
-      <c r="F115" s="89" t="s">
+      <c r="D118" s="25"/>
+      <c r="F118" s="98" t="s">
         <v>172</v>
       </c>
-      <c r="G115" s="21"/>
-      <c r="H115" s="33"/>
-    </row>
-    <row r="116" spans="2:8">
-      <c r="B116" s="32"/>
-      <c r="C116" s="89" t="s">
-        <v>30</v>
-      </c>
-      <c r="D116" s="21"/>
-      <c r="F116" s="89" t="s">
+      <c r="G118" s="25"/>
+      <c r="H118" s="85"/>
+    </row>
+    <row r="119" spans="2:8">
+      <c r="B119" s="100"/>
+      <c r="C119" s="58"/>
+      <c r="D119" s="58"/>
+      <c r="E119" s="58"/>
+      <c r="F119" s="98" t="s">
         <v>173</v>
       </c>
-      <c r="G116" s="21"/>
-      <c r="H116" s="33"/>
-    </row>
-    <row r="117" spans="2:8">
-      <c r="B117" s="32"/>
-      <c r="C117" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="D117" s="21"/>
-      <c r="F117" s="89" t="s">
+      <c r="G119" s="25"/>
+      <c r="H119" s="41"/>
+    </row>
+    <row r="121" spans="2:4">
+      <c r="B121" s="30" t="s">
         <v>174</v>
       </c>
-      <c r="G117" s="21"/>
-      <c r="H117" s="33"/>
-    </row>
-    <row r="118" spans="2:7">
-      <c r="B118" s="32"/>
-      <c r="C118" s="89" t="s">
+      <c r="C121" s="99" t="s">
         <v>175</v>
       </c>
-      <c r="D118" s="21"/>
-      <c r="F118" s="89" t="s">
+      <c r="D121" s="23"/>
+    </row>
+    <row r="122" spans="2:9">
+      <c r="B122" s="34"/>
+      <c r="C122" s="99" t="s">
         <v>176</v>
       </c>
-      <c r="G118" s="21"/>
-    </row>
-    <row r="119" spans="2:8">
-      <c r="B119" s="90"/>
-      <c r="C119" s="67"/>
-      <c r="D119" s="67"/>
-      <c r="E119" s="67"/>
-      <c r="F119" s="89" t="s">
+      <c r="D122" s="23"/>
+      <c r="F122" s="99" t="s">
+        <v>159</v>
+      </c>
+      <c r="G122" s="25"/>
+      <c r="H122" s="99" t="s">
         <v>177</v>
       </c>
-      <c r="G119" s="21"/>
-      <c r="H119" s="68"/>
-    </row>
-    <row r="121" spans="2:4">
-      <c r="B121" s="29" t="s">
+      <c r="I122" s="102"/>
+    </row>
+    <row r="123" spans="2:9">
+      <c r="B123" s="34"/>
+      <c r="C123" s="99" t="s">
         <v>178</v>
       </c>
-      <c r="C121" s="89" t="s">
+      <c r="D123" s="23"/>
+      <c r="F123" s="99" t="s">
+        <v>160</v>
+      </c>
+      <c r="G123" s="25"/>
+      <c r="H123" s="99" t="s">
         <v>179</v>
       </c>
-      <c r="D121" s="23"/>
-    </row>
-    <row r="122" spans="2:9">
-      <c r="B122" s="32"/>
-      <c r="C122" s="89" t="s">
+      <c r="I123" s="102"/>
+    </row>
+    <row r="124" spans="2:9">
+      <c r="B124" s="34"/>
+      <c r="C124" s="99" t="s">
         <v>180</v>
       </c>
-      <c r="D122" s="23"/>
-      <c r="F122" s="89" t="s">
-        <v>163</v>
-      </c>
-      <c r="G122" s="21"/>
-      <c r="H122" s="89" t="s">
+      <c r="D124" s="23"/>
+      <c r="F124" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="G124" s="25"/>
+      <c r="H124" s="99" t="s">
         <v>181</v>
       </c>
-      <c r="I122" s="92"/>
-    </row>
-    <row r="123" spans="2:9">
-      <c r="B123" s="32"/>
-      <c r="C123" s="89" t="s">
+      <c r="I124" s="102"/>
+    </row>
+    <row r="125" spans="2:9">
+      <c r="B125" s="34"/>
+      <c r="C125" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="D123" s="23"/>
-      <c r="F123" s="89" t="s">
-        <v>164</v>
-      </c>
-      <c r="G123" s="21"/>
-      <c r="H123" s="89" t="s">
+      <c r="D125" s="23"/>
+      <c r="F125" s="99" t="s">
         <v>183</v>
       </c>
-      <c r="I123" s="92"/>
-    </row>
-    <row r="124" spans="2:9">
-      <c r="B124" s="32"/>
-      <c r="C124" s="89" t="s">
+      <c r="G125" s="25"/>
+      <c r="H125" s="99" t="s">
         <v>184</v>
       </c>
-      <c r="D124" s="23"/>
-      <c r="F124" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="G124" s="21"/>
-      <c r="H124" s="89" t="s">
+      <c r="I125" s="102"/>
+    </row>
+    <row r="126" spans="2:9">
+      <c r="B126" s="100"/>
+      <c r="C126" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="I124" s="92"/>
-    </row>
-    <row r="125" spans="2:9">
-      <c r="B125" s="32"/>
-      <c r="C125" s="89" t="s">
+      <c r="D126" s="23"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="99" t="s">
         <v>186</v>
       </c>
-      <c r="D125" s="23"/>
-      <c r="F125" s="89" t="s">
+      <c r="G126" s="25"/>
+      <c r="H126" s="99" t="s">
         <v>187</v>
       </c>
-      <c r="G125" s="21"/>
-      <c r="H125" s="89" t="s">
+      <c r="I126" s="102"/>
+    </row>
+    <row r="128" spans="2:4">
+      <c r="B128" s="40" t="s">
         <v>188</v>
       </c>
-      <c r="I125" s="92"/>
-    </row>
-    <row r="126" spans="2:9">
-      <c r="B126" s="90"/>
-      <c r="C126" s="89" t="s">
+      <c r="C128" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="D126" s="23"/>
-      <c r="E126" s="67"/>
-      <c r="F126" s="89" t="s">
+      <c r="D128" s="35"/>
+    </row>
+    <row r="129" spans="2:4">
+      <c r="B129" s="42" t="s">
         <v>190</v>
       </c>
-      <c r="G126" s="21"/>
-      <c r="H126" s="89" t="s">
+      <c r="C129" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I126" s="92"/>
-    </row>
-    <row r="128" spans="2:4">
-      <c r="B128" s="37" t="s">
+      <c r="D129" s="35"/>
+    </row>
+    <row r="130" spans="2:4">
+      <c r="B130" s="44"/>
+      <c r="C130" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="C128" s="21" t="s">
+      <c r="D130" s="35"/>
+    </row>
+    <row r="132" spans="2:9">
+      <c r="B132" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D128" s="15"/>
-    </row>
-    <row r="129" spans="2:4">
-      <c r="B129" s="39" t="s">
+      <c r="C132" s="102"/>
+      <c r="D132" s="25"/>
+      <c r="E132" s="25"/>
+      <c r="F132" s="102"/>
+      <c r="G132" s="25"/>
+      <c r="H132" s="25"/>
+      <c r="I132" s="25"/>
+    </row>
+    <row r="133" spans="2:9">
+      <c r="B133" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C129" s="21" t="s">
+      <c r="C133" s="25"/>
+      <c r="D133" s="25"/>
+      <c r="E133" s="25"/>
+      <c r="F133" s="25"/>
+      <c r="G133" s="25"/>
+      <c r="H133" s="25"/>
+      <c r="I133" s="25"/>
+    </row>
+    <row r="134" spans="2:9">
+      <c r="B134" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="D129" s="15"/>
-    </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="41"/>
-      <c r="C130" s="21" t="s">
+      <c r="C134" s="103"/>
+      <c r="D134" s="103"/>
+      <c r="E134" s="103"/>
+      <c r="F134" s="103"/>
+      <c r="G134" s="25"/>
+      <c r="H134" s="25"/>
+      <c r="I134" s="25"/>
+    </row>
+    <row r="135" spans="2:9">
+      <c r="B135" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="D130" s="15"/>
-    </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="21" t="s">
+      <c r="C135" s="25"/>
+      <c r="D135" s="25"/>
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+      <c r="H135" s="25"/>
+      <c r="I135" s="25"/>
+    </row>
+    <row r="136" spans="2:9">
+      <c r="B136" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="C132" s="93"/>
-      <c r="F132" s="93"/>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133" s="21" t="s">
+      <c r="C136" s="25"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="25"/>
+      <c r="F136" s="25"/>
+      <c r="G136" s="25"/>
+      <c r="H136" s="25"/>
+      <c r="I136" s="25"/>
+    </row>
+    <row r="137" spans="2:9">
+      <c r="B137" s="21" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="134" spans="2:6">
-      <c r="B134" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="C134" s="94"/>
-      <c r="D134" s="94"/>
-      <c r="E134" s="94"/>
-      <c r="F134" s="94"/>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" s="21" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="136" spans="2:2">
-      <c r="B136" s="21" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="C137" s="94"/>
-      <c r="D137" s="94"/>
+      <c r="C137" s="103"/>
+      <c r="D137" s="103"/>
+      <c r="E137" s="25"/>
+      <c r="F137" s="25"/>
+      <c r="G137" s="25"/>
+      <c r="H137" s="25"/>
+      <c r="I137" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="B70:N70"/>
@@ -3868,11 +3842,11 @@
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="E51:E55"/>
     <mergeCell ref="E90:E97"/>
+    <mergeCell ref="N4:N10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3923,6 +3897,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="30" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="14.8981481481481" customWidth="1"/>
+    <col min="4" max="4" width="9.66666666666667" customWidth="1"/>
+    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="8" max="8" width="17.7777777777778" customWidth="1"/>
+    <col min="9" max="9" width="15.8611111111111" customWidth="1"/>
+    <col min="10" max="10" width="30.9351851851852" style="5" customWidth="1"/>
+    <col min="11" max="11" width="22.5833333333333" style="5" customWidth="1"/>
+    <col min="14" max="14" width="32.212962962963" style="5" customWidth="1"/>
+    <col min="15" max="15" width="13.7777777777778" customWidth="1"/>
+    <col min="16" max="16" width="11.8981481481481" customWidth="1"/>
+    <col min="19" max="19" width="16.537037037037" style="7" customWidth="1"/>
+    <col min="20" max="20" width="17.5555555555556" style="7" customWidth="1"/>
+    <col min="21" max="21" width="20.5" customWidth="1"/>
+    <col min="22" max="22" width="26.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="8.89814814814815" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="22.9166666666667" customWidth="1"/>
@@ -3944,7 +3945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
@@ -3955,7 +3956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
@@ -4003,7 +4004,18 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
